--- a/ig/acknowledgement/StructureDefinition-medcom-messaging-acknowledgementHeader.xlsx
+++ b/ig/acknowledgement/StructureDefinition-medcom-messaging-acknowledgementHeader.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="439">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.2</t>
+    <t>2.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T12:26:02+01:00</t>
+    <t>2026-02-05T13:48:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -478,20 +478,10 @@
     <t>Drives the behavior associated with this message.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>One of the message events defined as part of this version of FHIR.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/message-events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://medcomfhir.dk/ig/terminology/ValueSet/medcom-messaging-messageTypes</t>
   </si>
   <si>
     <t>MSH-9.2</t>
@@ -501,24 +491,6 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding</t>
-  </si>
-  <si>
-    <t>eventCoding</t>
-  </si>
-  <si>
-    <t>Code for the event this message represents or link to event definition</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://medcomfhir.dk/ig/terminology/ValueSet/medcom-messaging-messageTypes</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding.id</t>
   </si>
   <si>
     <t>MessageHeader.event[x].id</t>
@@ -540,9 +512,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.extension</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].extension</t>
   </si>
   <si>
@@ -562,9 +531,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.system</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].system</t>
   </si>
   <si>
@@ -589,9 +555,6 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.version</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].version</t>
   </si>
   <si>
@@ -613,9 +576,6 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.code</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].code</t>
   </si>
   <si>
@@ -637,9 +597,6 @@
     <t>./code</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.display</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].display</t>
   </si>
   <si>
@@ -659,9 +616,6 @@
   </si>
   <si>
     <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding.userSelected</t>
   </si>
   <si>
     <t>MessageHeader.event[x].userSelected</t>
@@ -715,6 +669,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>./communicationFunction[typeCode="RCV"]</t>
   </si>
   <si>
@@ -863,6 +820,9 @@
     <t>MessageHeader.destination:primary.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:primary.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:primary.extension:use</t>
   </si>
   <si>
@@ -909,15 +869,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding</t>
-  </si>
-  <si>
-    <t>valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -926,19 +877,22 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.id</t>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:primary.extension:use.value[x].id</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].id</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.extension</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].extension</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].extension</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.system</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].system</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].system</t>
@@ -947,25 +901,25 @@
     <t>http://medcomfhir.dk/ig/terminology/CodeSystem/medcom-messaging-destinationUse</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.version</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].version</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].version</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.code</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].code</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].code</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.display</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].display</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].display</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].userSelected</t>
@@ -1002,6 +956,9 @@
     <t>MessageHeader.destination:cc.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:cc.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:cc.extension:use</t>
   </si>
   <si>
@@ -1015,9 +972,6 @@
   </si>
   <si>
     <t>MessageHeader.destination:cc.extension:use.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1026,25 +980,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.id</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.extension</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.system</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.version</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.code</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.display</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:cc.extension:use.value[x].id</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].extension</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].system</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].version</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].code</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].display</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination:cc.modifierExtension</t>
@@ -1267,6 +1221,9 @@
   </si>
   <si>
     <t>Need to be able to track why resources are being changed and report in the audit log/history of the resource.  May affect authorization.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Reason for event occurrence.</t>
@@ -1731,20 +1688,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM91"/>
+  <dimension ref="A1:AM90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="77.984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.1171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.6875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.6953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="112.33984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="96.703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1753,25 +1710,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.98828125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="26.125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.8046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="28.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.90625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="23.56640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.28125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="160.15234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="140.38671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2002,7 +1959,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -2444,7 +2401,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -2890,7 +2847,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2909,7 +2866,7 @@
         <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>75</v>
@@ -2957,24 +2914,24 @@
       <c r="X11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="Y11" s="2"/>
+      <c r="Z11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Z11" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="AA11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>142</v>
@@ -2992,59 +2949,53 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>75</v>
       </c>
@@ -3068,11 +3019,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -3090,10 +3043,10 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>85</v>
@@ -3102,35 +3055,35 @@
         <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>75</v>
@@ -3142,15 +3095,17 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -3187,37 +3142,37 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>75</v>
@@ -3225,21 +3180,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
@@ -3248,21 +3203,23 @@
         <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
       </c>
@@ -3298,37 +3255,37 @@
         <v>75</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>75</v>
@@ -3336,10 +3293,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3362,20 +3319,18 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>75</v>
       </c>
@@ -3423,7 +3378,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3438,10 +3393,10 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>75</v>
@@ -3449,10 +3404,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3460,7 +3415,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>85</v>
@@ -3475,18 +3430,18 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
       </c>
@@ -3534,7 +3489,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3549,10 +3504,10 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>75</v>
@@ -3560,10 +3515,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3571,7 +3526,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>85</v>
@@ -3586,17 +3541,17 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>75</v>
@@ -3645,7 +3600,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3660,10 +3615,10 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>75</v>
@@ -3671,10 +3626,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3697,17 +3652,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3756,7 +3713,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3771,10 +3728,10 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>75</v>
@@ -3782,10 +3739,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3793,10 +3750,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>75</v>
@@ -3808,19 +3765,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3857,25 +3814,23 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>75</v>
@@ -3884,21 +3839,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3906,10 +3861,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>75</v>
@@ -3918,23 +3873,19 @@
         <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3970,46 +3921,48 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4017,10 +3970,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4032,13 +3985,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4077,50 +4030,50 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
@@ -4129,10 +4082,10 @@
         <v>85</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>75</v>
@@ -4141,13 +4094,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4186,17 +4139,19 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4205,7 +4160,7 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>136</v>
@@ -4222,44 +4177,46 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
@@ -4307,7 +4264,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4316,7 +4273,7 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>136</v>
@@ -4325,7 +4282,7 @@
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
@@ -4333,45 +4290,43 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4420,25 +4375,25 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -4446,10 +4401,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4472,17 +4427,17 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4531,7 +4486,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4546,10 +4501,10 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>75</v>
@@ -4557,10 +4512,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4568,7 +4523,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>85</v>
@@ -4583,17 +4538,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4642,10 +4599,10 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>85</v>
@@ -4657,10 +4614,10 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
@@ -4668,10 +4625,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4679,7 +4636,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>85</v>
@@ -4694,19 +4651,17 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4755,10 +4710,10 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>85</v>
@@ -4770,35 +4725,37 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
@@ -4807,17 +4764,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4866,13 +4825,13 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>75</v>
@@ -4881,59 +4840,53 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4981,47 +4934,47 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>226</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -5033,15 +4986,17 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5078,51 +5033,49 @@
         <v>75</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -5144,13 +5097,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5201,7 +5154,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5210,7 +5163,7 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>136</v>
@@ -5227,10 +5180,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5253,13 +5206,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5310,7 +5263,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5328,7 +5281,7 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>75</v>
@@ -5336,10 +5289,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5365,10 +5318,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5407,19 +5360,19 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5445,10 +5398,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5474,13 +5427,13 @@
         <v>99</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5488,7 +5441,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>75</v>
@@ -5530,7 +5483,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>85</v>
@@ -5556,10 +5509,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5585,10 +5538,10 @@
         <v>143</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5600,7 +5553,7 @@
         <v>75</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>75</v>
+        <v>275</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>75</v>
@@ -5627,17 +5580,19 @@
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5663,20 +5618,18 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>85</v>
@@ -5691,13 +5644,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>155</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
+        <v>156</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5709,7 +5662,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -5748,7 +5701,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>157</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5760,13 +5713,13 @@
         <v>75</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
@@ -5774,21 +5727,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -5800,15 +5753,17 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5845,37 +5800,37 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -5883,21 +5838,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5906,21 +5861,23 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5929,7 +5886,7 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>75</v>
@@ -5956,37 +5913,37 @@
         <v>75</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AC38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>75</v>
@@ -5994,10 +5951,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6020,20 +5977,18 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -6042,7 +5997,7 @@
         <v>75</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>298</v>
+        <v>75</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>75</v>
@@ -6081,7 +6036,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6096,10 +6051,10 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
@@ -6107,10 +6062,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6133,18 +6088,18 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -6192,7 +6147,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6207,10 +6162,10 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -6218,10 +6173,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6244,17 +6199,17 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6303,7 +6258,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6318,10 +6273,10 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -6329,10 +6284,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6355,17 +6310,19 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6414,7 +6371,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6429,10 +6386,10 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -6440,45 +6397,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>223</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6527,25 +6484,25 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6553,45 +6510,43 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6640,25 +6595,25 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -6666,10 +6621,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6692,17 +6647,17 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6751,7 +6706,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6766,21 +6721,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>246</v>
+        <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6788,13 +6743,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6803,17 +6758,19 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6862,10 +6819,10 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>85</v>
@@ -6877,21 +6834,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6914,19 +6871,17 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6975,10 +6930,10 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>85</v>
@@ -6990,35 +6945,37 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>75</v>
@@ -7027,17 +6984,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>312</v>
+        <v>204</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>313</v>
+        <v>205</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7086,13 +7045,13 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -7101,25 +7060,23 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7128,7 +7085,7 @@
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -7137,23 +7094,19 @@
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7201,47 +7154,47 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>226</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -7253,15 +7206,17 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7298,51 +7253,49 @@
         <v>75</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>75</v>
@@ -7364,13 +7317,13 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7421,7 +7374,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7430,7 +7383,7 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>136</v>
@@ -7447,10 +7400,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7473,13 +7426,13 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7530,7 +7483,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7548,7 +7501,7 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>75</v>
@@ -7556,10 +7509,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7585,10 +7538,10 @@
         <v>131</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7627,19 +7580,19 @@
         <v>75</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7665,10 +7618,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7694,13 +7647,13 @@
         <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7708,7 +7661,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>75</v>
@@ -7750,7 +7703,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>85</v>
@@ -7776,10 +7729,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7805,10 +7758,10 @@
         <v>143</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7820,7 +7773,7 @@
         <v>75</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>75</v>
@@ -7847,17 +7800,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7883,20 +7838,18 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>85</v>
@@ -7911,13 +7864,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>286</v>
+        <v>155</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>287</v>
+        <v>156</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7929,7 +7882,7 @@
         <v>75</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>75</v>
@@ -7968,7 +7921,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>288</v>
+        <v>157</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7980,13 +7933,13 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>75</v>
@@ -7994,21 +7947,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -8020,15 +7973,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8065,37 +8020,37 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>75</v>
@@ -8103,21 +8058,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
@@ -8126,21 +8081,23 @@
         <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -8149,7 +8106,7 @@
         <v>75</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>75</v>
@@ -8176,37 +8133,37 @@
         <v>75</v>
       </c>
       <c r="AB58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK58" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AC58" t="s" s="2">
+      <c r="AL58" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>75</v>
@@ -8214,10 +8171,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8240,20 +8197,18 @@
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8262,7 +8217,7 @@
         <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>298</v>
+        <v>75</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>75</v>
@@ -8301,7 +8256,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8316,10 +8271,10 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>75</v>
@@ -8327,10 +8282,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8353,18 +8308,18 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
       </c>
@@ -8412,7 +8367,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8427,10 +8382,10 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>75</v>
@@ -8438,10 +8393,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8464,17 +8419,17 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8523,7 +8478,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8538,10 +8493,10 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>75</v>
@@ -8549,10 +8504,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8575,17 +8530,19 @@
         <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8634,7 +8591,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8649,10 +8606,10 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -8660,45 +8617,45 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>306</v>
+        <v>223</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -8747,25 +8704,25 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
@@ -8773,45 +8730,43 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8860,25 +8815,25 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -8886,10 +8841,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8912,17 +8867,17 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8971,7 +8926,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8986,21 +8941,21 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>246</v>
+        <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9008,13 +8963,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>75</v>
@@ -9023,17 +8978,19 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9082,10 +9039,10 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>85</v>
@@ -9097,21 +9054,21 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9134,19 +9091,17 @@
         <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -9195,10 +9150,10 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>85</v>
@@ -9210,21 +9165,21 @@
         <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9247,17 +9202,19 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9306,7 +9263,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9321,21 +9278,21 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9343,13 +9300,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
@@ -9358,19 +9315,19 @@
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9419,7 +9376,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9434,21 +9391,21 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>226</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9471,19 +9428,19 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9532,7 +9489,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9547,21 +9504,21 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9569,13 +9526,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
@@ -9584,19 +9541,17 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -9645,10 +9600,10 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>85</v>
@@ -9660,21 +9615,21 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9682,33 +9637,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>356</v>
+        <v>155</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>357</v>
+        <v>156</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>358</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>75</v>
       </c>
@@ -9756,10 +9709,10 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>355</v>
+        <v>157</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>85</v>
@@ -9768,35 +9721,35 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>359</v>
+        <v>158</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>75</v>
@@ -9808,15 +9761,17 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9865,25 +9820,25 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>75</v>
@@ -9891,14 +9846,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9911,24 +9866,26 @@
         <v>75</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -9976,7 +9933,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -9994,7 +9951,7 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>75</v>
@@ -10002,45 +9959,43 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>140</v>
+        <v>351</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10089,25 +10044,25 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>241</v>
+        <v>349</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>128</v>
+        <v>353</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>75</v>
@@ -10115,10 +10070,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10141,17 +10096,17 @@
         <v>86</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>243</v>
+        <v>355</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>75</v>
@@ -10200,7 +10155,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10215,10 +10170,10 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
@@ -10226,10 +10181,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10252,17 +10207,17 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10311,7 +10266,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10326,10 +10281,10 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>75</v>
@@ -10337,10 +10292,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10363,17 +10318,17 @@
         <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -10422,7 +10377,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10437,21 +10392,21 @@
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10459,13 +10414,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>75</v>
@@ -10474,17 +10429,19 @@
         <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>381</v>
+        <v>241</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10533,10 +10490,10 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>85</v>
@@ -10548,10 +10505,10 @@
         <v>97</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>75</v>
@@ -10559,10 +10516,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10570,13 +10527,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -10585,19 +10542,19 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>258</v>
+        <v>330</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10646,10 +10603,10 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>85</v>
@@ -10661,21 +10618,21 @@
         <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10698,19 +10655,17 @@
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>263</v>
+        <v>385</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10735,13 +10690,13 @@
         <v>75</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>75</v>
+        <v>391</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>75</v>
@@ -10759,7 +10714,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10774,21 +10729,21 @@
         <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10796,13 +10751,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>75</v>
@@ -10811,18 +10766,16 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>400</v>
+        <v>204</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>403</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
@@ -10846,13 +10799,13 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>404</v>
+        <v>75</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>405</v>
+        <v>75</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -10870,7 +10823,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10885,21 +10838,21 @@
         <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>408</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10907,28 +10860,28 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>410</v>
+        <v>155</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>411</v>
+        <v>156</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10979,7 +10932,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>409</v>
+        <v>157</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10991,13 +10944,13 @@
         <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>412</v>
+        <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>413</v>
+        <v>158</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>75</v>
@@ -11005,21 +10958,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -11031,15 +10984,17 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11088,25 +11043,25 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>75</v>
@@ -11114,14 +11069,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11134,24 +11089,26 @@
         <v>75</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
       </c>
@@ -11199,7 +11156,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11217,53 +11174,51 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>239</v>
+        <v>404</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>140</v>
+        <v>406</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -11312,36 +11267,36 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>241</v>
+        <v>403</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>75</v>
+        <v>407</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>128</v>
+        <v>408</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11364,17 +11319,19 @@
         <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -11399,13 +11356,13 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>75</v>
+        <v>415</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -11423,7 +11380,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>85</v>
@@ -11438,21 +11395,21 @@
         <v>97</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11460,7 +11417,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>85</v>
@@ -11475,19 +11432,19 @@
         <v>86</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>105</v>
+        <v>419</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11512,13 +11469,13 @@
         <v>75</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>429</v>
+        <v>75</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -11536,10 +11493,10 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>85</v>
@@ -11551,10 +11508,10 @@
         <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>75</v>
@@ -11562,10 +11519,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11576,10 +11533,10 @@
         <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>75</v>
@@ -11588,19 +11545,19 @@
         <v>86</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11649,13 +11606,13 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>75</v>
@@ -11664,10 +11621,10 @@
         <v>97</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>438</v>
+        <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -11675,10 +11632,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11689,7 +11646,7 @@
         <v>76</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>75</v>
@@ -11701,19 +11658,17 @@
         <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -11762,13 +11717,13 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>75</v>
@@ -11780,135 +11735,24 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AM91" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM91">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AM90">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
